--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\hoc tap\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hoc_tap\DATN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9049B233-8835-4292-B043-675F901E4403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA8142E-CDE7-4B3B-BB5E-E6ECB4E3A751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{2116B685-F135-47D6-B1D5-9A2A2D157225}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2116B685-F135-47D6-B1D5-9A2A2D157225}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -71,6 +71,9 @@
     <t>Hệ quản trị CSDL</t>
   </si>
   <si>
+    <t>21115053120105</t>
+  </si>
+  <si>
     <t>LÊ HÀ</t>
   </si>
   <si>
@@ -78,9 +81,6 @@
   </si>
   <si>
     <t>0862910409</t>
-  </si>
-  <si>
-    <t>21115053120105</t>
   </si>
   <si>
     <t>Xậy dựng website mạng xã hội cho UTE tích hợp tính năng tích điểm để khuyến khích sinh viên tham gia hoạt động của trường</t>
@@ -89,15 +89,18 @@
     <t xml:space="preserve"> Xem bài viết dăng bài viết 
  Nhắn tin, tạo cuộc gọi
  Đăng bài kèm sự kiên cho phép sinh viên đăng ký tham gia
- Sinh viên điểm danh trong sự kiện bằng cách 
-</t>
+ Sinh viên điểm danh trong sự kiện bằng cách đưa mã QR điểm danh của bản thân cho người phụ trách điểm danh quét: 
+      Hiện tại em sẽ sử dụng 3 cách thức để hạn chế tôi đa trường hợp gian lận trong việc điểm danh:
+                1. Là Sử dụng công nghệ xác nhận vị trí của người quét mã QR và người được quét mã QR: Geolib hoặc HTML5 Geolocation API
+                2. Là thông tin cá nhân (mã sinh viên, họ và tên, ảnh thẻ ) khi tạo mã QR để điểm danh sẽ được hiện thị để người điểm danh có thêm cơ sở để xác thực người đó có đúng người hay không
+ Còn về việc sinh viên có thể đi về giữa chừng thì em có thể gửi mail xác định vị trí để so sánh với vị trí cuối cùng so với vị trí đầu tiên lúc điểm danh nếu quá xa thì cho là điểm danh thất bại (mail này em sẽ gửi ngẫu nhiện một nhóm nhỏ trong những sinh viên tham gia sự kiện thôi)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -584,18 +587,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D99CB8E8-F25D-4F95-9DA9-4AB4DF5C951E}">
   <dimension ref="A1:X2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="27.69921875" customWidth="1"/>
     <col min="3" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" customWidth="1"/>
+    <col min="5" max="5" width="16.09765625" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="87.88671875" customWidth="1"/>
+    <col min="7" max="7" width="87.8984375" customWidth="1"/>
     <col min="8" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="90" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" ht="90" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,21 +648,21 @@
       <c r="W1" s="3"/>
       <c r="X1" s="3"/>
     </row>
-    <row r="2" spans="1:24" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" ht="171.6">
       <c r="A2" s="4">
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>13</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>15</v>
